--- a/data/trans_orig/P35A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023</t>
+          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53398</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114352</t>
+          <t>115727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152183</t>
+          <t>154341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80162</t>
+          <t>81026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109514</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202038</t>
+          <t>199923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251505</t>
+          <t>249385</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314557</t>
+          <t>314172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>355894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>316106</t>
+          <t>317037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642325</t>
+          <t>641579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>697708</t>
+          <t>693789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69333</t>
+          <t>71405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45857</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103850</t>
+          <t>103249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141768</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73877</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102969</t>
+          <t>100443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183934</t>
+          <t>184387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234366</t>
+          <t>231492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252133</t>
+          <t>254973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>296526</t>
+          <t>297296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>247935</t>
+          <t>248212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278794</t>
+          <t>279152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>510650</t>
+          <t>510694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562962</t>
+          <t>565599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>55341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68868</t>
+          <t>66114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176588</t>
+          <t>174377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>561839</t>
+          <t>545208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>43518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229644</t>
+          <t>230418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>658306</t>
+          <t>643967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417118</t>
+          <t>421338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89675</t>
+          <t>90310</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110046</t>
+          <t>110625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149878</t>
+          <t>163255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>519264</t>
+          <t>520357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68390</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110762</t>
+          <t>107238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91903</t>
+          <t>91260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162525</t>
+          <t>163989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26532</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>52826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239510</t>
+          <t>241471</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>296321</t>
+          <t>300351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92085</t>
+          <t>91876</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>229654</t>
+          <t>229528</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>312544</t>
+          <t>287518</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>511931</t>
+          <t>508586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>623726</t>
+          <t>624771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>692267</t>
+          <t>691934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>662941</t>
+          <t>662582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>843019</t>
+          <t>851331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1309614</t>
+          <t>1311195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1585055</t>
+          <t>1606822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65478</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84510</t>
+          <t>83691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>129036</t>
+          <t>128785</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>49338</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>83846</t>
+          <t>84884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119167</t>
+          <t>120270</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>183723</t>
+          <t>187666</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>283224</t>
+          <t>284713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284846</t>
+          <t>288107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>388907</t>
+          <t>383934</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>294092</t>
+          <t>291819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>336659</t>
+          <t>333394</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>464390</t>
+          <t>462064</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>601189</t>
+          <t>592472</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>776571</t>
+          <t>776298</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>916466</t>
+          <t>908928</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60147</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>92276</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80557</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>122229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>53090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>177336</t>
+          <t>177393</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>219268</t>
+          <t>218249</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>191366</t>
+          <t>190325</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>241796</t>
+          <t>238277</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169822</t>
+          <t>169863</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>208961</t>
+          <t>208100</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>433829</t>
+          <t>434938</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>485139</t>
+          <t>481114</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>614799</t>
+          <t>616340</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>680512</t>
+          <t>683867</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>196383</t>
+          <t>194012</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>291522</t>
+          <t>289379</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>186705</t>
+          <t>186670</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>258600</t>
+          <t>261771</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>408176</t>
+          <t>410562</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>536954</t>
+          <t>537155</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>65563</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>105909</t>
+          <t>105669</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>79881</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>118515</t>
+          <t>117905</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>151968</t>
+          <t>154804</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>212429</t>
+          <t>212415</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>799632</t>
+          <t>801928</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1525266</t>
+          <t>1436681</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>704984</t>
+          <t>708052</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>932912</t>
+          <t>929388</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1628468</t>
+          <t>1613963</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2551531</t>
+          <t>2480035</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1593735</t>
+          <t>1658541</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2214045</t>
+          <t>2217535</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2293646</t>
+          <t>2295790</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2605044</t>
+          <t>2600457</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3858360</t>
+          <t>3907349</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4656139</t>
+          <t>4682336</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>41943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>43538</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>59339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132509</t>
+          <t>151261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>129626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154341</t>
+          <t>173670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>106062</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81026</t>
+          <t>90039</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107386</t>
+          <t>121691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>225976</t>
+          <t>257323</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199923</t>
+          <t>232399</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249385</t>
+          <t>286916</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>336295</t>
+          <t>360055</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314172</t>
+          <t>337976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355894</t>
+          <t>384878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>331959</t>
+          <t>358220</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>317037</t>
+          <t>341646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346506</t>
+          <t>375105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>668254</t>
+          <t>718275</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>641579</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>693789</t>
+          <t>745574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35593</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49432</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>55295</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71405</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>36539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>127671</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103249</t>
+          <t>109127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141633</t>
+          <t>147919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86985</t>
+          <t>96577</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72351</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100443</t>
+          <t>112697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>207634</t>
+          <t>224248</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184387</t>
+          <t>199869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231492</t>
+          <t>249640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>275239</t>
+          <t>290424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254973</t>
+          <t>268110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297296</t>
+          <t>314570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>263152</t>
+          <t>290454</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>248212</t>
+          <t>273630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279152</t>
+          <t>307566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>538391</t>
+          <t>580877</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>510694</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>565599</t>
+          <t>606055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>36668</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55341</t>
+          <t>49323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66114</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>360191</t>
+          <t>126291</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174377</t>
+          <t>108437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>545208</t>
+          <t>143795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62796</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>412852</t>
+          <t>184676</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230418</t>
+          <t>164624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>643967</t>
+          <t>206081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>291164</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>270778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421338</t>
+          <t>310732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100700</t>
+          <t>113534</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90310</t>
+          <t>101897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110625</t>
+          <t>124116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>361187</t>
+          <t>404699</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163255</t>
+          <t>382051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>520357</t>
+          <t>427541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>97954</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68326</t>
+          <t>79258</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107238</t>
+          <t>124046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>75858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>156674</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>132360</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163989</t>
+          <t>184729</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52826</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268966</t>
+          <t>290703</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>241471</t>
+          <t>264504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>300351</t>
+          <t>324310</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>174994</t>
+          <t>195666</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91876</t>
+          <t>175482</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>229528</t>
+          <t>217523</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>443960</t>
+          <t>486369</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>287518</t>
+          <t>449292</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>508586</t>
+          <t>525660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>659271</t>
+          <t>718117</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>624771</t>
+          <t>682159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>691934</t>
+          <t>751186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>735012</t>
+          <t>586481</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>662582</t>
+          <t>563338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>851331</t>
+          <t>609841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1394282</t>
+          <t>1304598</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1311195</t>
+          <t>1260274</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1606822</t>
+          <t>1346940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,22 +3001,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48076</t>
+          <t>55051</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>41881</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66042</t>
+          <t>72146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>59009</t>
+          <t>67584</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43384</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>82911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>107085</t>
+          <t>122634</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>105387</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>128785</t>
+          <t>144499</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>41750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38162</t>
+          <t>45282</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49338</t>
+          <t>58924</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>101337</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84884</t>
+          <t>91717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120270</t>
+          <t>129104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>247040</t>
+          <t>271450</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>187666</t>
+          <t>249584</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>284713</t>
+          <t>295324</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>348377</t>
+          <t>380779</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288107</t>
+          <t>352067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383934</t>
+          <t>411977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>314301</t>
+          <t>390053</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>291819</t>
+          <t>364608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>333394</t>
+          <t>411485</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>508456</t>
+          <t>460067</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>462064</t>
+          <t>434995</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>592472</t>
+          <t>484003</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>822757</t>
+          <t>850119</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>776298</t>
+          <t>818011</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>908928</t>
+          <t>884787</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>89307</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60402</t>
+          <t>71713</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>111919</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>98322</t>
+          <t>119495</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>78536</t>
+          <t>98127</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>122229</t>
+          <t>145986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>34897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22720</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>196788</t>
+          <t>216081</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>177393</t>
+          <t>194723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>218249</t>
+          <t>239024</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>214686</t>
+          <t>235463</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>190325</t>
+          <t>210475</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>262495</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>191626</t>
+          <t>180247</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169863</t>
+          <t>157426</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>208100</t>
+          <t>196860</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>458833</t>
+          <t>503586</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>434938</t>
+          <t>477296</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>481114</t>
+          <t>530679</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>650460</t>
+          <t>683834</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>616340</t>
+          <t>647765</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>683867</t>
+          <t>716530</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>760966</t>
+          <t>843871</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>760966</t>
+          <t>843871</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>760966</t>
+          <t>843871</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001474</t>
+          <t>1081099</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001474</t>
+          <t>1081099</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001474</t>
+          <t>1081099</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>252056</t>
+          <t>290505</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>194012</t>
+          <t>253771</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>289379</t>
+          <t>328187</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>227582</t>
+          <t>265215</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>186670</t>
+          <t>237747</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>261771</t>
+          <t>296863</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>479639</t>
+          <t>555720</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>410562</t>
+          <t>509582</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>537155</t>
+          <t>601703</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>85237</t>
+          <t>97275</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>65563</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>105669</t>
+          <t>120974</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>79789</t>
+          <t>95568</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>117905</t>
+          <t>130151</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>184395</t>
+          <t>209885</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>154804</t>
+          <t>185688</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>212415</t>
+          <t>235225</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1001548</t>
+          <t>824636</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>801928</t>
+          <t>775123</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1436681</t>
+          <t>873844</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>851936</t>
+          <t>944220</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>708052</t>
+          <t>904167</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>929388</t>
+          <t>991065</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1853484</t>
+          <t>1768857</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1613963</t>
+          <t>1706086</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2480035</t>
+          <t>1839483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2037219</t>
+          <t>2230060</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1658541</t>
+          <t>2172575</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2217535</t>
+          <t>2288840</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,67 +4513,67 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2398112</t>
+          <t>2312342</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2295790</t>
+          <t>2259371</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2600457</t>
+          <t>2360693</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>62,17%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>64,95%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>4542402</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>4470591</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4612526</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>64,19%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>72,7%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>5309</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>4435330</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>3907349</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>4682336</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>63,79%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3576788</t>
+          <t>3634388</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3576788</t>
+          <t>3634388</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3576788</t>
+          <t>3634388</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6952848</t>
+          <t>7076864</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6952848</t>
+          <t>7076864</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6952848</t>
+          <t>7076864</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
